--- a/order_forms/023_university_educational_tool_order_form--order_forms.xlsx
+++ b/order_forms/023_university_educational_tool_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>submitted_by_1</t>
+          <t>submitted by 1</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>submitted_by_2</t>
+          <t>submitted by 2</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>submitted_by_2_1</t>
+          <t>submitted by 2 1</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>submitted_by_2_2</t>
+          <t>submitted by 2 2</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>tool_type_1</t>
+          <t>tool type 1</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>tool_type_2</t>
+          <t>tool type 2</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>tool_status_1</t>
+          <t>tool status 1</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>tool_status_2</t>
+          <t>tool status 2</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>submitter_1</t>
+          <t>submitter 1</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>submitter_2</t>
+          <t>submitter 2</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>tool_name_1</t>
+          <t>tool name 1</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>tool_name_2</t>
+          <t>tool name 2</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>submitter_department_1</t>
+          <t>submitter department 1</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>submitter_department_2</t>
+          <t>submitter department 2</t>
         </is>
       </c>
     </row>
